--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,60 +1045,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133697489</v>
+        <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>96780</v>
+        <v>97583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>535</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>325565</v>
+        <v>325393</v>
       </c>
       <c r="R5" t="n">
-        <v>6557419</v>
+        <v>6557916</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1122,17 +1110,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Östsluttning mot myr</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,84 +1124,71 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697489</t>
+          <t>https://artportalen.se/Sighting/136707248</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133697616</v>
+        <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>96780</v>
+        <v>97583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>535</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranodontium denudatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brid.) E.Britton</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>325619</v>
+        <v>325407</v>
       </c>
       <c r="R6" t="n">
-        <v>6557333</v>
+        <v>6557900</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1242,12 +1212,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,76 +1226,71 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697616</t>
+          <t>https://artportalen.se/Sighting/136707249</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133696761</v>
+        <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>96783</v>
+        <v>97583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>325401</v>
+        <v>325489</v>
       </c>
       <c r="R7" t="n">
-        <v>6557930</v>
+        <v>6557773</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,12 +1314,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,76 +1328,71 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696761</t>
+          <t>https://artportalen.se/Sighting/136707252</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133696898</v>
+        <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97810</v>
+        <v>97583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>325388</v>
+        <v>325545</v>
       </c>
       <c r="R8" t="n">
-        <v>6557926</v>
+        <v>6557558</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,12 +1416,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,76 +1430,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696898</t>
+          <t>https://artportalen.se/Sighting/136707261</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133697534</v>
+        <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97810</v>
+        <v>97583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>325609</v>
+        <v>325565</v>
       </c>
       <c r="R9" t="n">
-        <v>6557373</v>
+        <v>6557554</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,12 +1518,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,83 +1532,71 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697534</t>
+          <t>https://artportalen.se/Sighting/136707262</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133696982</v>
+        <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>97583</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sydost Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>325668</v>
+        <v>325582</v>
       </c>
       <c r="R10" t="n">
-        <v>6557541</v>
+        <v>6557532</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,12 +1620,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,61 +1634,69 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696982</t>
+          <t>https://artportalen.se/Sighting/136707263</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133697491</v>
+        <v>133697489</v>
       </c>
       <c r="B11" t="n">
-        <v>75468</v>
+        <v>96780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>535</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1791,6 +1742,11 @@
           <t>2026-05-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Östsluttning mot myr</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1815,54 +1771,63 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697491</t>
+          <t>https://artportalen.se/Sighting/133697489</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133698127</v>
+        <v>133697616</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>96780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>535</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Söder Lilla Lekarvall, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>325663</v>
+        <v>325619</v>
       </c>
       <c r="R12" t="n">
-        <v>6557566</v>
+        <v>6557333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,11 +1862,6 @@
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På hård kärnved av naturlig tallhögstubbe i exponerat läge.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1926,16 +1886,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133698127</t>
+          <t>https://artportalen.se/Sighting/133697616</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133696697</v>
+        <v>133696761</v>
       </c>
       <c r="B13" t="n">
-        <v>4776</v>
+        <v>96783</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1943,32 +1903,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>2180</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1976,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>325411</v>
+        <v>325401</v>
       </c>
       <c r="R13" t="n">
-        <v>6557937</v>
+        <v>6557930</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2038,16 +1993,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696697</t>
+          <t>https://artportalen.se/Sighting/133696761</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133697670</v>
+        <v>133696898</v>
       </c>
       <c r="B14" t="n">
-        <v>4776</v>
+        <v>97810</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2055,43 +2010,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Norr Skäktetjärnen, Dls</t>
+          <t>Norr Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>325636</v>
+        <v>325388</v>
       </c>
       <c r="R14" t="n">
-        <v>6557254</v>
+        <v>6557926</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,16 +2100,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697670</t>
+          <t>https://artportalen.se/Sighting/133696898</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133698197</v>
+        <v>133697534</v>
       </c>
       <c r="B15" t="n">
-        <v>4776</v>
+        <v>97810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2167,43 +2117,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>SSO Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>325432</v>
+        <v>325609</v>
       </c>
       <c r="R15" t="n">
-        <v>6557678</v>
+        <v>6557373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,69 +2201,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Gran, Martin  Sjöberg</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133698197</t>
+          <t>https://artportalen.se/Sighting/133697534</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133696875</v>
+        <v>136707250</v>
       </c>
       <c r="B16" t="n">
-        <v>5181</v>
+        <v>93404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Norr Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>325375</v>
+        <v>325421</v>
       </c>
       <c r="R16" t="n">
-        <v>6557928</v>
+        <v>6557872</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2342,12 +2278,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,34 +2292,33 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696875</t>
+          <t>https://artportalen.se/Sighting/136707250</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133697451</v>
+        <v>136707256</v>
       </c>
       <c r="B17" t="n">
-        <v>5181</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,46 +2326,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>325576</v>
+        <v>325502</v>
       </c>
       <c r="R17" t="n">
-        <v>6557448</v>
+        <v>6557689</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2454,12 +2380,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,34 +2394,48 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697451</t>
+          <t>https://artportalen.se/Sighting/136707256</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133697666</v>
+        <v>136707259</v>
       </c>
       <c r="B18" t="n">
-        <v>5181</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,46 +2443,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norr Skäktetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>325636</v>
+        <v>325531</v>
       </c>
       <c r="R18" t="n">
-        <v>6557254</v>
+        <v>6557648</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2566,12 +2497,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,81 +2511,86 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697666</t>
+          <t>https://artportalen.se/Sighting/136707259</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133698192</v>
+        <v>136707251</v>
       </c>
       <c r="B19" t="n">
-        <v>5181</v>
+        <v>93430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>5448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>Mellanfjällen, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>325432</v>
+        <v>325489</v>
       </c>
       <c r="R19" t="n">
-        <v>6557678</v>
+        <v>6557773</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2678,12 +2614,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2692,81 +2628,79 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Gran</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133698192</t>
+          <t>https://artportalen.se/Sighting/136707251</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133697512</v>
+        <v>133696982</v>
       </c>
       <c r="B20" t="n">
-        <v>58461</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SSO Kuvetjärnen, Dls</t>
+          <t>Sydost Kuvetjärnen, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>325565</v>
+        <v>325668</v>
       </c>
       <c r="R20" t="n">
-        <v>6557419</v>
+        <v>6557541</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2807,6 +2741,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2824,49 +2759,43 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697512</t>
+          <t>https://artportalen.se/Sighting/133696982</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133697454</v>
+        <v>133697491</v>
       </c>
       <c r="B21" t="n">
-        <v>5201</v>
+        <v>75468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2874,10 +2803,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>325576</v>
+        <v>325565</v>
       </c>
       <c r="R21" t="n">
-        <v>6557448</v>
+        <v>6557419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2936,59 +2865,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133697454</t>
+          <t>https://artportalen.se/Sighting/133697491</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134287731</v>
+        <v>133698127</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kuvetjärnen, Dls</t>
+          <t>Söder Lilla Lekarvall, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>325514</v>
+        <v>325663</v>
       </c>
       <c r="R22" t="n">
-        <v>6557642</v>
+        <v>6557566</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3015,12 +2939,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På hård kärnved av naturlig tallhögstubbe i exponerat läge.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3033,26 +2962,1966 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bård E. Andersen</t>
+          <t>Roger Gran</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133698127</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133696697</v>
+      </c>
+      <c r="B23" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norr Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>325411</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6557937</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696697</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>133697670</v>
+      </c>
+      <c r="B24" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norr Skäktetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>325636</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6557254</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697670</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>133698197</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4776</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325432</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6557678</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Roger Gran, Martin  Sjöberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698197</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136707257</v>
+      </c>
+      <c r="B26" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>325502</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6557689</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707257</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136707260</v>
+      </c>
+      <c r="B27" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>325531</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6557648</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707260</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>133696875</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norr Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>325375</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6557928</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133696875</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>133697451</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>325576</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6557448</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697451</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>133697666</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norr Skäktetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>325636</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6557254</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697666</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>133698192</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>325432</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6557678</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133698192</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>133697512</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>325565</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6557419</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697512</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>133697454</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SSO Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>325576</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6557448</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133697454</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136707247</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>325393</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6557916</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707247</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136707253</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>325512</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6557748</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707253</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136707255</v>
+      </c>
+      <c r="B36" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>325502</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6557689</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707255</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134287731</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kuvetjärnen, Dls</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>325514</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6557642</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bård E. Andersen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134287731</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136707258</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99346</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>325543</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6557654</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707258</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136707246</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>325369</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6557960</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707246</t>
         </is>
       </c>
     </row>
@@ -3079,6 +4948,23 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>136707250</v>
       </c>
       <c r="B16" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>136707256</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136707259</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136707251</v>
       </c>
       <c r="B19" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>136707258</v>
       </c>
       <c r="B38" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>136707246</v>
       </c>
       <c r="B39" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>136707250</v>
       </c>
       <c r="B16" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>136707256</v>
       </c>
       <c r="B17" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>136707259</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>136707251</v>
       </c>
       <c r="B19" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>136707258</v>
       </c>
       <c r="B38" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>136707246</v>
       </c>
       <c r="B39" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97965</v>
+        <v>97971</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92170</v>
+        <v>92172</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97971</v>
+        <v>97973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92172</v>
+        <v>92174</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -8779,7 +8779,7 @@
         <v>133696697</v>
       </c>
       <c r="B77" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>133697670</v>
       </c>
       <c r="B78" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>133698197</v>
       </c>
       <c r="B79" t="n">
-        <v>4776</v>
+        <v>4777</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>133696875</v>
       </c>
       <c r="B93" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>133697451</v>
       </c>
       <c r="B94" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
         <v>133697666</v>
       </c>
       <c r="B95" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11037,7 +11037,7 @@
         <v>133698192</v>
       </c>
       <c r="B96" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97973</v>
+        <v>97974</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92174</v>
+        <v>92175</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97974</v>
+        <v>97980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92175</v>
+        <v>92181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97980</v>
+        <v>97984</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92185</v>
+        <v>92187</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>97988</v>
+        <v>98001</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92187</v>
+        <v>92200</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136890152</v>
       </c>
       <c r="B62" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>136890154</v>
       </c>
       <c r="B63" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>136890159</v>
       </c>
       <c r="B64" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>136890162</v>
       </c>
       <c r="B65" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>136890167</v>
       </c>
       <c r="B66" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136890170</v>
       </c>
       <c r="B67" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>136890173</v>
       </c>
       <c r="B68" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>136890175</v>
       </c>
       <c r="B69" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>136890180</v>
       </c>
       <c r="B70" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>136890182</v>
       </c>
       <c r="B71" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>136890184</v>
       </c>
       <c r="B72" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>136890185</v>
       </c>
       <c r="B73" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>136890187</v>
       </c>
       <c r="B74" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98001</v>
+        <v>98003</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92200</v>
+        <v>92202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136890152</v>
       </c>
       <c r="B62" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>136890154</v>
       </c>
       <c r="B63" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>136890159</v>
       </c>
       <c r="B64" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>136890162</v>
       </c>
       <c r="B65" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>136890167</v>
       </c>
       <c r="B66" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136890170</v>
       </c>
       <c r="B67" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>136890173</v>
       </c>
       <c r="B68" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>136890175</v>
       </c>
       <c r="B69" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>136890180</v>
       </c>
       <c r="B70" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>136890182</v>
       </c>
       <c r="B71" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>136890184</v>
       </c>
       <c r="B72" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>136890185</v>
       </c>
       <c r="B73" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>136890187</v>
       </c>
       <c r="B74" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>136890148</v>
       </c>
       <c r="B130" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>136890190</v>
       </c>
       <c r="B131" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>136890247</v>
       </c>
       <c r="B132" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -8808,11 +8808,7 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8920,11 +8916,7 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9032,11 +9024,7 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9141,11 +9129,7 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9263,11 +9247,7 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9385,11 +9365,7 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9507,11 +9483,7 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9629,11 +9601,7 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9751,11 +9719,7 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9873,11 +9837,7 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -9995,11 +9955,7 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10117,11 +10073,7 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10239,11 +10191,7 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10361,11 +10309,7 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10483,11 +10427,7 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10605,11 +10545,7 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -10730,11 +10666,7 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10842,11 +10774,7 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10954,11 +10882,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11066,11 +10990,7 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11175,11 +11095,7 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11297,11 +11213,7 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11419,11 +11331,7 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11541,11 +11449,7 @@
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11663,11 +11567,7 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11785,11 +11685,7 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -11907,11 +11803,7 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12029,11 +11921,7 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12151,11 +12039,7 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12273,11 +12157,7 @@
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12395,11 +12275,7 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12860,11 +12736,7 @@
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -12982,11 +12854,7 @@
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13104,11 +12972,7 @@
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13226,11 +13090,7 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13348,11 +13208,7 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13470,11 +13326,7 @@
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13592,11 +13444,7 @@
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13714,11 +13562,7 @@
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13836,11 +13680,7 @@
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -13958,11 +13798,7 @@
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14080,11 +13916,7 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14202,11 +14034,7 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14324,11 +14152,7 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14446,11 +14270,7 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14568,11 +14388,7 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14690,11 +14506,7 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14812,11 +14624,7 @@
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -14934,11 +14742,7 @@
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -15056,11 +14860,7 @@
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98003</v>
+        <v>98006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92202</v>
+        <v>92205</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>136707248</v>
       </c>
       <c r="B5" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>136707249</v>
       </c>
       <c r="B6" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>136707252</v>
       </c>
       <c r="B7" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136707261</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>136707262</v>
       </c>
       <c r="B9" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>136707263</v>
       </c>
       <c r="B10" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98006</v>
+        <v>98016</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>136707250</v>
       </c>
       <c r="B35" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92205</v>
+        <v>92215</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>136707256</v>
       </c>
       <c r="B49" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136707259</v>
       </c>
       <c r="B50" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>136707251</v>
       </c>
       <c r="B55" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136890152</v>
       </c>
       <c r="B62" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>136890154</v>
       </c>
       <c r="B63" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>136890159</v>
       </c>
       <c r="B64" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>136890162</v>
       </c>
       <c r="B65" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>136890167</v>
       </c>
       <c r="B66" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136890170</v>
       </c>
       <c r="B67" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>136890173</v>
       </c>
       <c r="B68" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>136890175</v>
       </c>
       <c r="B69" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>136890180</v>
       </c>
       <c r="B70" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>136890182</v>
       </c>
       <c r="B71" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>136890184</v>
       </c>
       <c r="B72" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>136890185</v>
       </c>
       <c r="B73" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>136890187</v>
       </c>
       <c r="B74" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>133696697</v>
       </c>
       <c r="B77" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>133697670</v>
       </c>
       <c r="B78" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>133698197</v>
       </c>
       <c r="B79" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>136707257</v>
       </c>
       <c r="B80" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>136707260</v>
       </c>
       <c r="B81" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>136890112</v>
       </c>
       <c r="B82" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>136890135</v>
       </c>
       <c r="B83" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>136890147</v>
       </c>
       <c r="B84" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>136890169</v>
       </c>
       <c r="B85" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>136890181</v>
       </c>
       <c r="B86" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>136890200</v>
       </c>
       <c r="B87" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>136890201</v>
       </c>
       <c r="B88" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>136890205</v>
       </c>
       <c r="B89" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136890207</v>
       </c>
       <c r="B90" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>136890213</v>
       </c>
       <c r="B91" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>136890218</v>
       </c>
       <c r="B92" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>133696875</v>
       </c>
       <c r="B93" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>133697451</v>
       </c>
       <c r="B94" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>133697666</v>
       </c>
       <c r="B95" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10961,7 +10961,7 @@
         <v>133698192</v>
       </c>
       <c r="B96" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>136890114</v>
       </c>
       <c r="B97" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>136890151</v>
       </c>
       <c r="B98" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>136890177</v>
       </c>
       <c r="B99" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>136890186</v>
       </c>
       <c r="B100" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>136890188</v>
       </c>
       <c r="B101" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>136890194</v>
       </c>
       <c r="B102" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>136890204</v>
       </c>
       <c r="B103" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>136890208</v>
       </c>
       <c r="B104" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>136890223</v>
       </c>
       <c r="B105" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>136890226</v>
       </c>
       <c r="B106" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         <v>136890228</v>
       </c>
       <c r="B107" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>136890166</v>
       </c>
       <c r="B108" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12710,7 +12710,7 @@
         <v>136707247</v>
       </c>
       <c r="B111" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>136707253</v>
       </c>
       <c r="B112" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>136707255</v>
       </c>
       <c r="B113" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>136890115</v>
       </c>
       <c r="B114" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13182,7 +13182,7 @@
         <v>136890145</v>
       </c>
       <c r="B115" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
         <v>136890146</v>
       </c>
       <c r="B116" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>136890150</v>
       </c>
       <c r="B117" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>136890183</v>
       </c>
       <c r="B118" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>136890189</v>
       </c>
       <c r="B119" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>136890193</v>
       </c>
       <c r="B120" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>136890195</v>
       </c>
       <c r="B121" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>136890202</v>
       </c>
       <c r="B122" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>136890203</v>
       </c>
       <c r="B123" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14244,7 +14244,7 @@
         <v>136890206</v>
       </c>
       <c r="B124" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14362,7 +14362,7 @@
         <v>136890209</v>
       </c>
       <c r="B125" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>136890215</v>
       </c>
       <c r="B126" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>136890222</v>
       </c>
       <c r="B127" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>136890225</v>
       </c>
       <c r="B128" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>136890227</v>
       </c>
       <c r="B129" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>136890148</v>
       </c>
       <c r="B130" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>136890190</v>
       </c>
       <c r="B131" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>136890247</v>
       </c>
       <c r="B132" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15374,7 +15374,7 @@
         <v>136707258</v>
       </c>
       <c r="B134" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15597,7 +15597,7 @@
         <v>136707246</v>
       </c>
       <c r="B136" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98016</v>
+        <v>98017</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98017</v>
+        <v>98022</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92216</v>
+        <v>92219</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>136890152</v>
       </c>
       <c r="B62" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>136890154</v>
       </c>
       <c r="B63" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>136890159</v>
       </c>
       <c r="B64" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>136890162</v>
       </c>
       <c r="B65" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         <v>136890167</v>
       </c>
       <c r="B66" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>136890170</v>
       </c>
       <c r="B67" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>136890173</v>
       </c>
       <c r="B68" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>136890175</v>
       </c>
       <c r="B69" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>136890180</v>
       </c>
       <c r="B70" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>136890182</v>
       </c>
       <c r="B71" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8200,7 +8200,7 @@
         <v>136890184</v>
       </c>
       <c r="B72" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>136890185</v>
       </c>
       <c r="B73" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>136890187</v>
       </c>
       <c r="B74" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
         <v>136890171</v>
       </c>
       <c r="B76" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>136890172</v>
       </c>
       <c r="B135" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/A 22932-2026 artfynd.xlsx
+++ b/artfynd/A 22932-2026 artfynd.xlsx
@@ -1660,7 +1660,7 @@
         <v>136890111</v>
       </c>
       <c r="B11" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>136890153</v>
       </c>
       <c r="B12" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         <v>136890155</v>
       </c>
       <c r="B13" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>136890157</v>
       </c>
       <c r="B14" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>136890158</v>
       </c>
       <c r="B15" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136890163</v>
       </c>
       <c r="B16" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>136890164</v>
       </c>
       <c r="B17" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>136890174</v>
       </c>
       <c r="B18" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>136890179</v>
       </c>
       <c r="B19" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>136890210</v>
       </c>
       <c r="B20" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         <v>136890211</v>
       </c>
       <c r="B21" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136890212</v>
       </c>
       <c r="B22" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
         <v>136890214</v>
       </c>
       <c r="B23" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>136890216</v>
       </c>
       <c r="B24" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>136890149</v>
       </c>
       <c r="B28" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>136890220</v>
       </c>
       <c r="B29" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>136890156</v>
       </c>
       <c r="B32" t="n">
-        <v>98022</v>
+        <v>98024</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>136890176</v>
       </c>
       <c r="B33" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>136890178</v>
       </c>
       <c r="B34" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         <v>136890110</v>
       </c>
       <c r="B36" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>136890138</v>
       </c>
       <c r="B37" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
         <v>136890139</v>
       </c>
       <c r="B38" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>136890141</v>
       </c>
       <c r="B39" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>136890142</v>
       </c>
       <c r="B40" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>136890191</v>
       </c>
       <c r="B41" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,7 +4868,7 @@
         <v>136890192</v>
       </c>
       <c r="B42" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>136890196</v>
       </c>
       <c r="B43" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>136890197</v>
       </c>
       <c r="B44" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>136890219</v>
       </c>
       <c r="B45" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
         <v>136890221</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
         <v>136890224</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>136890198</v>
       </c>
       <c r="B48" t="n">
-        <v>92219</v>
+        <v>92221</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>136890113</v>
       </c>
       <c r="B51" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>136890136</v>
       </c>
       <c r="B52" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>136890137</v>
       </c>
       <c r="B53" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>136890168</v>
       </c>
       <c r="B54" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>136890143</v>
       </c>
       <c r="B56" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>136890140</v>
       </c>
       <c r="B57" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>136890144</v>
       </c>
       <c r="B58" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6708,7 +6708,7 @@
         <v>136890199</v>
       </c>
       <c r="B59" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
